--- a/Result/profitability/2332.xlsx
+++ b/Result/profitability/2332.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM84"/>
+  <dimension ref="A1:AM85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,10 +667,10 @@
         <v>0.66</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02375000000000002</v>
+        <v>-0.06375000000000004</v>
       </c>
       <c r="N2" t="n">
-        <v>26.33625</v>
+        <v>25.5375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -776,10 +776,10 @@
         <v>0.42</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.008750000000000029</v>
+        <v>0.01249999999999997</v>
       </c>
       <c r="N3" t="n">
-        <v>26.47625</v>
+        <v>26.32875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -893,10 +893,10 @@
         <v>1.14</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1575</v>
+        <v>0.1899999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>27.16625</v>
+        <v>27.1625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1010,10 +1010,10 @@
         <v>0.59</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2662499999999999</v>
+        <v>0.2925</v>
       </c>
       <c r="N5" t="n">
-        <v>28.0275</v>
+        <v>27.9225</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1127,10 +1127,10 @@
         <v>0.99</v>
       </c>
       <c r="M6" t="n">
-        <v>0.41875</v>
+        <v>0.41375</v>
       </c>
       <c r="N6" t="n">
-        <v>28.9875</v>
+        <v>28.76875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1252,10 +1252,10 @@
         <v>0.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0.49125</v>
+        <v>0.54125</v>
       </c>
       <c r="N7" t="n">
-        <v>29.565</v>
+        <v>29.63875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1377,10 +1377,10 @@
         <v>1.08</v>
       </c>
       <c r="M8" t="n">
-        <v>0.67875</v>
+        <v>0.6824999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>30.5025</v>
+        <v>30.355</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1502,7 +1502,7 @@
         <v>1.23</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8387499999999999</v>
+        <v>0.83875</v>
       </c>
       <c r="N9" t="n">
         <v>31.84125</v>
@@ -1627,7 +1627,7 @@
         <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9749999999999999</v>
+        <v>0.975</v>
       </c>
       <c r="N10" t="n">
         <v>32.245</v>
@@ -2133,7 +2133,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9837499999999999</v>
+        <v>0.98375</v>
       </c>
       <c r="N14" t="n">
         <v>32.93</v>
@@ -11080,6 +11080,133 @@
       </c>
       <c r="AM84" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2332</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>3686</v>
+      </c>
+      <c r="D85" t="n">
+        <v>2798</v>
+      </c>
+      <c r="E85" t="n">
+        <v>888</v>
+      </c>
+      <c r="F85" t="n">
+        <v>24.09</v>
+      </c>
+      <c r="G85" t="n">
+        <v>66</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>1.80%</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J85" t="n">
+        <v>46</v>
+      </c>
+      <c r="K85" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L85" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M85" t="n">
+        <v>-0.10875</v>
+      </c>
+      <c r="N85" t="n">
+        <v>25.4375</v>
+      </c>
+      <c r="O85" t="n">
+        <v>1</v>
+      </c>
+      <c r="P85" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W85" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X85" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>-0.04669568658488321</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>-0.9130434782608696</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>-0.8399999999999999</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>-0.03369434416365824</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK85" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
